--- a/data/processed/harmonization/Isotopes__Soil_organic_carbon_delta13C/10.15485_1839288/10.15485_1839288_soil_Isotopes__Soil_organic_carbon_delta13C.xlsx
+++ b/data/processed/harmonization/Isotopes__Soil_organic_carbon_delta13C/10.15485_1839288/10.15485_1839288_soil_Isotopes__Soil_organic_carbon_delta13C.xlsx
@@ -518,12 +518,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:1:0-1</t>
+          <t>OUT_SHALLOW:0-1:1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -570,12 +570,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:1:1-2</t>
+          <t>OUT_SHALLOW:1-2:1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:1:2-3</t>
+          <t>OUT_SHALLOW:2-3:1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:1:3-4</t>
+          <t>OUT_SHALLOW:3-4:1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:1:4-5</t>
+          <t>OUT_SHALLOW:4-5:1</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:1:5-7</t>
+          <t>OUT_SHALLOW:5-7:1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:1:7-9</t>
+          <t>OUT_SHALLOW:7-9:1</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:1:9-11</t>
+          <t>OUT_SHALLOW:9-11:1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -934,12 +934,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:1:11-13</t>
+          <t>OUT_SHALLOW:11-13:1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:1:13-15</t>
+          <t>OUT_SHALLOW:13-15:1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:1:15-17</t>
+          <t>OUT_SHALLOW:15-17:1</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:1:17-19</t>
+          <t>OUT_SHALLOW:17-19:1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:1:19-21</t>
+          <t>OUT_SHALLOW:19-21:1</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:1:21-23</t>
+          <t>OUT_SHALLOW:21-23:1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:1:23-25</t>
+          <t>OUT_SHALLOW:23-25:1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:1:25-27</t>
+          <t>OUT_SHALLOW:25-27:1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:1:27-29</t>
+          <t>OUT_SHALLOW:27-29:1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:2:0-1</t>
+          <t>OUT_SHALLOW:0-1:2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:2:1-2</t>
+          <t>OUT_SHALLOW:1-2:2</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:2:2-3</t>
+          <t>OUT_SHALLOW:2-3:2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:2:3-4</t>
+          <t>OUT_SHALLOW:3-4:2</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:2:4-5</t>
+          <t>OUT_SHALLOW:4-5:2</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:2:5-7</t>
+          <t>OUT_SHALLOW:5-7:2</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:2:7-9</t>
+          <t>OUT_SHALLOW:7-9:2</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:2:9-11</t>
+          <t>OUT_SHALLOW:9-11:2</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:2:11-13</t>
+          <t>OUT_SHALLOW:11-13:2</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:2:13-15</t>
+          <t>OUT_SHALLOW:13-15:2</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:2:15-17</t>
+          <t>OUT_SHALLOW:15-17:2</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1974,12 +1974,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:2:17-19</t>
+          <t>OUT_SHALLOW:17-19:2</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:2:19-21</t>
+          <t>OUT_SHALLOW:19-21:2</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:2:21-23</t>
+          <t>OUT_SHALLOW:21-23:2</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:2:23-25</t>
+          <t>OUT_SHALLOW:23-25:2</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:2:25-27</t>
+          <t>OUT_SHALLOW:25-27:2</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:2:27-29</t>
+          <t>OUT_SHALLOW:27-29:2</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:3:0-1</t>
+          <t>OUT_SHALLOW:0-1:3</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:3:1-2</t>
+          <t>OUT_SHALLOW:1-2:3</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:3:2-3</t>
+          <t>OUT_SHALLOW:2-3:3</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:3:3-4</t>
+          <t>OUT_SHALLOW:3-4:3</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:3:4-5</t>
+          <t>OUT_SHALLOW:4-5:3</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:3:5-7</t>
+          <t>OUT_SHALLOW:5-7:3</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:3:7-9</t>
+          <t>OUT_SHALLOW:7-9:3</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:3:9-11</t>
+          <t>OUT_SHALLOW:9-11:3</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:3:11-13</t>
+          <t>OUT_SHALLOW:11-13:3</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:3:13-15</t>
+          <t>OUT_SHALLOW:13-15:3</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:3:15-17</t>
+          <t>OUT_SHALLOW:15-17:3</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:3:17-19</t>
+          <t>OUT_SHALLOW:17-19:3</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:3:19-21</t>
+          <t>OUT_SHALLOW:19-21:3</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:3:21-23</t>
+          <t>OUT_SHALLOW:21-23:3</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:3:23-25</t>
+          <t>OUT_SHALLOW:23-25:3</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3066,12 +3066,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:3:25-27</t>
+          <t>OUT_SHALLOW:25-27:3</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:3:27-29</t>
+          <t>OUT_SHALLOW:27-29:3</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:4:0-1</t>
+          <t>OUT_SHALLOW:0-1:4</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:4:1-2</t>
+          <t>OUT_SHALLOW:1-2:4</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:4:2-3</t>
+          <t>OUT_SHALLOW:2-3:4</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3326,12 +3326,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:4:3-4</t>
+          <t>OUT_SHALLOW:3-4:4</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:4:4-5</t>
+          <t>OUT_SHALLOW:4-5:4</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:4:5-7</t>
+          <t>OUT_SHALLOW:5-7:4</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:4:7-9</t>
+          <t>OUT_SHALLOW:7-9:4</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3534,12 +3534,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:4:9-11</t>
+          <t>OUT_SHALLOW:9-11:4</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:4:11-13</t>
+          <t>OUT_SHALLOW:11-13:4</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:4:13-15</t>
+          <t>OUT_SHALLOW:13-15:4</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:4:15-17</t>
+          <t>OUT_SHALLOW:15-17:4</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:4:17-19</t>
+          <t>OUT_SHALLOW:17-19:4</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:4:19-21</t>
+          <t>OUT_SHALLOW:19-21:4</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:4:21-23</t>
+          <t>OUT_SHALLOW:21-23:4</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:4:23-25</t>
+          <t>OUT_SHALLOW:23-25:4</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:4:25-27</t>
+          <t>OUT_SHALLOW:25-27:4</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>OUT_SHALLOW:4:27-29</t>
+          <t>OUT_SHALLOW:27-29:4</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:5:0-1</t>
+          <t>OUT_INTER:0-1:5</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:5:1-2</t>
+          <t>OUT_INTER:1-2:5</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:5:2-3</t>
+          <t>OUT_INTER:2-3:5</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:5:3-4</t>
+          <t>OUT_INTER:3-4:5</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -4262,12 +4262,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:5:4-5</t>
+          <t>OUT_INTER:4-5:5</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4314,12 +4314,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:5:5-7</t>
+          <t>OUT_INTER:5-7:5</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:5:7-9</t>
+          <t>OUT_INTER:7-9:5</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:5:9-11</t>
+          <t>OUT_INTER:9-11:5</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:5:11-13</t>
+          <t>OUT_INTER:11-13:5</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:5:13-15</t>
+          <t>OUT_INTER:13-15:5</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:5:15-17</t>
+          <t>OUT_INTER:15-17:5</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:5:17-19</t>
+          <t>OUT_INTER:17-19:5</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:5:19-21</t>
+          <t>OUT_INTER:19-21:5</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:5:21-23</t>
+          <t>OUT_INTER:21-23:5</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:5:23-25</t>
+          <t>OUT_INTER:23-25:5</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4834,12 +4834,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:5:25-27</t>
+          <t>OUT_INTER:25-27:5</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:5:27-29</t>
+          <t>OUT_INTER:27-29:5</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:6:0-1</t>
+          <t>OUT_INTER:0-1:6</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:6:1-2</t>
+          <t>OUT_INTER:1-2:6</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -5042,12 +5042,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:6:2-3</t>
+          <t>OUT_INTER:2-3:6</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:6:3-4</t>
+          <t>OUT_INTER:3-4:6</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:6:4-5</t>
+          <t>OUT_INTER:4-5:6</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:6:5-7</t>
+          <t>OUT_INTER:5-7:6</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:6:7-9</t>
+          <t>OUT_INTER:7-9:6</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:6:9-11</t>
+          <t>OUT_INTER:9-11:6</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:6:11-13</t>
+          <t>OUT_INTER:11-13:6</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:6:13-15</t>
+          <t>OUT_INTER:13-15:6</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5458,12 +5458,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:6:15-17</t>
+          <t>OUT_INTER:15-17:6</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:6:17-19</t>
+          <t>OUT_INTER:17-19:6</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:6:19-21</t>
+          <t>OUT_INTER:19-21:6</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:6:21-23</t>
+          <t>OUT_INTER:21-23:6</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:6:23-25</t>
+          <t>OUT_INTER:23-25:6</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5718,12 +5718,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:6:25-27</t>
+          <t>OUT_INTER:25-27:6</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:6:27-29</t>
+          <t>OUT_INTER:27-29:6</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:7:0-1</t>
+          <t>OUT_INTER:0-1:7</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:7:1-2</t>
+          <t>OUT_INTER:1-2:7</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:7:2-3</t>
+          <t>OUT_INTER:2-3:7</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:7:3-4</t>
+          <t>OUT_INTER:3-4:7</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:7:4-5</t>
+          <t>OUT_INTER:4-5:7</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:7:5-7</t>
+          <t>OUT_INTER:5-7:7</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:7:7-9</t>
+          <t>OUT_INTER:7-9:7</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:7:9-11</t>
+          <t>OUT_INTER:9-11:7</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:7:11-13</t>
+          <t>OUT_INTER:11-13:7</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -6290,12 +6290,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:7:13-15</t>
+          <t>OUT_INTER:13-15:7</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -6342,12 +6342,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:7:15-17</t>
+          <t>OUT_INTER:15-17:7</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:7:17-19</t>
+          <t>OUT_INTER:17-19:7</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6446,12 +6446,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:7:19-21</t>
+          <t>OUT_INTER:19-21:7</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:7:21-23</t>
+          <t>OUT_INTER:21-23:7</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:7:23-25</t>
+          <t>OUT_INTER:23-25:7</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:7:25-27</t>
+          <t>OUT_INTER:25-27:7</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:7:27-29</t>
+          <t>OUT_INTER:27-29:7</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:8:0-1</t>
+          <t>OUT_INTER:0-1:8</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:8:1-2</t>
+          <t>OUT_INTER:1-2:8</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:8:2-3</t>
+          <t>OUT_INTER:2-3:8</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6862,12 +6862,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:8:3-4</t>
+          <t>OUT_INTER:3-4:8</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:8:4-5</t>
+          <t>OUT_INTER:4-5:8</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:8:5-7</t>
+          <t>OUT_INTER:5-7:8</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -7018,12 +7018,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:8:7-9</t>
+          <t>OUT_INTER:7-9:8</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:8:9-11</t>
+          <t>OUT_INTER:9-11:8</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -7122,12 +7122,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:8:11-13</t>
+          <t>OUT_INTER:11-13:8</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:8:13-15</t>
+          <t>OUT_INTER:13-15:8</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -7226,12 +7226,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:8:15-17</t>
+          <t>OUT_INTER:15-17:8</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -7278,12 +7278,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:8:17-19</t>
+          <t>OUT_INTER:17-19:8</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:8:19-21</t>
+          <t>OUT_INTER:19-21:8</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:8:21-23</t>
+          <t>OUT_INTER:21-23:8</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -7434,12 +7434,12 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:8:23-25</t>
+          <t>OUT_INTER:23-25:8</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:8:25-27</t>
+          <t>OUT_INTER:25-27:8</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>OUT_INTER:8:27-29</t>
+          <t>OUT_INTER:27-29:8</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:9:0-1</t>
+          <t>OUT_DEEP:0-1:9</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:9:1-2</t>
+          <t>OUT_DEEP:1-2:9</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:9:2-3</t>
+          <t>OUT_DEEP:2-3:9</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:9:3-4</t>
+          <t>OUT_DEEP:3-4:9</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:9:4-5</t>
+          <t>OUT_DEEP:4-5:9</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:9:5-7</t>
+          <t>OUT_DEEP:5-7:9</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:9:7-9</t>
+          <t>OUT_DEEP:7-9:9</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:9:9-11</t>
+          <t>OUT_DEEP:9-11:9</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:9:11-13</t>
+          <t>OUT_DEEP:11-13:9</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -8058,12 +8058,12 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:9:13-15</t>
+          <t>OUT_DEEP:13-15:9</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:9:15-17</t>
+          <t>OUT_DEEP:15-17:9</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:9:17-19</t>
+          <t>OUT_DEEP:17-19:9</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:9:19-21</t>
+          <t>OUT_DEEP:19-21:9</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:9:21-23</t>
+          <t>OUT_DEEP:21-23:9</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -8318,12 +8318,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:9:23-25</t>
+          <t>OUT_DEEP:23-25:9</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:9:25-27</t>
+          <t>OUT_DEEP:25-27:9</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:9:27-29</t>
+          <t>OUT_DEEP:27-29:9</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -8474,12 +8474,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:10:0-1</t>
+          <t>OUT_DEEP:0-1:10</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:10:1-2</t>
+          <t>OUT_DEEP:1-2:10</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -8578,12 +8578,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:10:2-3</t>
+          <t>OUT_DEEP:2-3:10</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -8630,12 +8630,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:10:3-4</t>
+          <t>OUT_DEEP:3-4:10</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:10:4-5</t>
+          <t>OUT_DEEP:4-5:10</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:10:5-7</t>
+          <t>OUT_DEEP:5-7:10</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:10:7-9</t>
+          <t>OUT_DEEP:7-9:10</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:10:9-11</t>
+          <t>OUT_DEEP:9-11:10</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:10:11-13</t>
+          <t>OUT_DEEP:11-13:10</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -8942,12 +8942,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:10:13-15</t>
+          <t>OUT_DEEP:13-15:10</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:10:15-17</t>
+          <t>OUT_DEEP:15-17:10</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -9046,12 +9046,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:10:17-19</t>
+          <t>OUT_DEEP:17-19:10</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -9098,12 +9098,12 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:10:19-21</t>
+          <t>OUT_DEEP:19-21:10</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:10:21-23</t>
+          <t>OUT_DEEP:21-23:10</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:10:23-25</t>
+          <t>OUT_DEEP:23-25:10</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:10:25-27</t>
+          <t>OUT_DEEP:25-27:10</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -9306,12 +9306,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:10:27-29</t>
+          <t>OUT_DEEP:27-29:10</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -9358,12 +9358,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:11:0-1</t>
+          <t>OUT_DEEP:0-1:11</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -9410,12 +9410,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:11:1-2</t>
+          <t>OUT_DEEP:1-2:11</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:11:2-3</t>
+          <t>OUT_DEEP:2-3:11</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -9514,12 +9514,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:11:3-4</t>
+          <t>OUT_DEEP:3-4:11</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -9566,12 +9566,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:11:4-5</t>
+          <t>OUT_DEEP:4-5:11</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:11:5-7</t>
+          <t>OUT_DEEP:5-7:11</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:11:7-9</t>
+          <t>OUT_DEEP:7-9:11</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:11:9-11</t>
+          <t>OUT_DEEP:9-11:11</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -9774,12 +9774,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:11:11-13</t>
+          <t>OUT_DEEP:11-13:11</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -9826,12 +9826,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:11:13-15</t>
+          <t>OUT_DEEP:13-15:11</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:11:15-17</t>
+          <t>OUT_DEEP:15-17:11</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -9930,12 +9930,12 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:11:17-19</t>
+          <t>OUT_DEEP:17-19:11</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:11:19-21</t>
+          <t>OUT_DEEP:19-21:11</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:11:21-23</t>
+          <t>OUT_DEEP:21-23:11</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:11:23-25</t>
+          <t>OUT_DEEP:23-25:11</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:11:25-27</t>
+          <t>OUT_DEEP:25-27:11</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:11:27-29</t>
+          <t>OUT_DEEP:27-29:11</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:12:0-1</t>
+          <t>OUT_DEEP:0-1:12</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -10294,12 +10294,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:12:1-2</t>
+          <t>OUT_DEEP:1-2:12</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -10346,12 +10346,12 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:12:2-3</t>
+          <t>OUT_DEEP:2-3:12</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -10398,12 +10398,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:12:3-4</t>
+          <t>OUT_DEEP:3-4:12</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:12:4-5</t>
+          <t>OUT_DEEP:4-5:12</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:12:5-7</t>
+          <t>OUT_DEEP:5-7:12</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:12:7-9</t>
+          <t>OUT_DEEP:7-9:12</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -10606,12 +10606,12 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:12:9-11</t>
+          <t>OUT_DEEP:9-11:12</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -10658,12 +10658,12 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:12:11-13</t>
+          <t>OUT_DEEP:11-13:12</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:12:13-15</t>
+          <t>OUT_DEEP:13-15:12</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -10762,12 +10762,12 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:12:15-17</t>
+          <t>OUT_DEEP:15-17:12</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:12:17-19</t>
+          <t>OUT_DEEP:17-19:12</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:12:19-21</t>
+          <t>OUT_DEEP:19-21:12</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -10918,12 +10918,12 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:12:21-23</t>
+          <t>OUT_DEEP:21-23:12</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -10970,12 +10970,12 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:12:23-25</t>
+          <t>OUT_DEEP:23-25:12</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:12:25-27</t>
+          <t>OUT_DEEP:25-27:12</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -11074,12 +11074,12 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>OUT_DEEP:12:27-29</t>
+          <t>OUT_DEEP:27-29:12</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -11126,12 +11126,12 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:13:0-1</t>
+          <t>BACK_SHALLOW:0-1:13</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -11178,12 +11178,12 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:13:1-2</t>
+          <t>BACK_SHALLOW:1-2:13</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:13:2-3</t>
+          <t>BACK_SHALLOW:2-3:13</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:13:3-4</t>
+          <t>BACK_SHALLOW:3-4:13</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -11334,12 +11334,12 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:13:4-5</t>
+          <t>BACK_SHALLOW:4-5:13</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -11386,12 +11386,12 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:13:5-7</t>
+          <t>BACK_SHALLOW:5-7:13</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:13:7-9</t>
+          <t>BACK_SHALLOW:7-9:13</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -11490,12 +11490,12 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:13:9-11</t>
+          <t>BACK_SHALLOW:9-11:13</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -11542,12 +11542,12 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:13:11-13</t>
+          <t>BACK_SHALLOW:11-13:13</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -11594,12 +11594,12 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:13:13-15</t>
+          <t>BACK_SHALLOW:13-15:13</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -11646,12 +11646,12 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:13:15-17</t>
+          <t>BACK_SHALLOW:15-17:13</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -11698,12 +11698,12 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:13:17-19</t>
+          <t>BACK_SHALLOW:17-19:13</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -11750,12 +11750,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:13:19-21</t>
+          <t>BACK_SHALLOW:19-21:13</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:13:21-23</t>
+          <t>BACK_SHALLOW:21-23:13</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:13:23-25</t>
+          <t>BACK_SHALLOW:23-25:13</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -11906,12 +11906,12 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:13:25-27</t>
+          <t>BACK_SHALLOW:25-27:13</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:13:27-29</t>
+          <t>BACK_SHALLOW:27-29:13</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:14:0-1</t>
+          <t>BACK_SHALLOW:0-1:14</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:14:1-2</t>
+          <t>BACK_SHALLOW:1-2:14</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -12114,12 +12114,12 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:14:2-3</t>
+          <t>BACK_SHALLOW:2-3:14</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -12166,12 +12166,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:14:3-4</t>
+          <t>BACK_SHALLOW:3-4:14</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:14:4-5</t>
+          <t>BACK_SHALLOW:4-5:14</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -12270,12 +12270,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:14:5-7</t>
+          <t>BACK_SHALLOW:5-7:14</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -12322,12 +12322,12 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:14:7-9</t>
+          <t>BACK_SHALLOW:7-9:14</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -12374,12 +12374,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:14:9-11</t>
+          <t>BACK_SHALLOW:9-11:14</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:14:11-13</t>
+          <t>BACK_SHALLOW:11-13:14</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -12478,12 +12478,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:14:13-15</t>
+          <t>BACK_SHALLOW:13-15:14</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -12530,12 +12530,12 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:14:15-17</t>
+          <t>BACK_SHALLOW:15-17:14</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:14:17-19</t>
+          <t>BACK_SHALLOW:17-19:14</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:14:19-21</t>
+          <t>BACK_SHALLOW:19-21:14</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -12686,12 +12686,12 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:14:21-23</t>
+          <t>BACK_SHALLOW:21-23:14</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -12738,12 +12738,12 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:14:23-25</t>
+          <t>BACK_SHALLOW:23-25:14</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -12790,12 +12790,12 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:14:25-27</t>
+          <t>BACK_SHALLOW:25-27:14</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:14:27-29</t>
+          <t>BACK_SHALLOW:27-29:14</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -12894,12 +12894,12 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:15:0-1</t>
+          <t>BACK_SHALLOW:0-1:15</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -12946,12 +12946,12 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:15:1-2</t>
+          <t>BACK_SHALLOW:1-2:15</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:15:2-3</t>
+          <t>BACK_SHALLOW:2-3:15</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -13050,12 +13050,12 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:15:3-4</t>
+          <t>BACK_SHALLOW:3-4:15</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -13102,12 +13102,12 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:15:4-5</t>
+          <t>BACK_SHALLOW:4-5:15</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:15:5-7</t>
+          <t>BACK_SHALLOW:5-7:15</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:15:7-9</t>
+          <t>BACK_SHALLOW:7-9:15</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:15:9-11</t>
+          <t>BACK_SHALLOW:9-11:15</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -13310,12 +13310,12 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:15:11-13</t>
+          <t>BACK_SHALLOW:11-13:15</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -13362,12 +13362,12 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:15:13-15</t>
+          <t>BACK_SHALLOW:13-15:15</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:15:15-17</t>
+          <t>BACK_SHALLOW:15-17:15</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -13466,12 +13466,12 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:15:17-19</t>
+          <t>BACK_SHALLOW:17-19:15</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -13518,12 +13518,12 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:15:19-21</t>
+          <t>BACK_SHALLOW:19-21:15</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -13570,12 +13570,12 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:15:21-23</t>
+          <t>BACK_SHALLOW:21-23:15</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -13622,12 +13622,12 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:15:23-25</t>
+          <t>BACK_SHALLOW:23-25:15</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:15:25-27</t>
+          <t>BACK_SHALLOW:25-27:15</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -13726,12 +13726,12 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:15:27-29</t>
+          <t>BACK_SHALLOW:27-29:15</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -13778,12 +13778,12 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:16:0-1</t>
+          <t>BACK_SHALLOW:0-1:16</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:16:1-2</t>
+          <t>BACK_SHALLOW:1-2:16</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -13882,12 +13882,12 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:16:2-3</t>
+          <t>BACK_SHALLOW:2-3:16</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -13934,12 +13934,12 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:16:3-4</t>
+          <t>BACK_SHALLOW:3-4:16</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -13986,12 +13986,12 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:16:4-5</t>
+          <t>BACK_SHALLOW:4-5:16</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -14038,12 +14038,12 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:16:5-7</t>
+          <t>BACK_SHALLOW:5-7:16</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -14090,12 +14090,12 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:16:7-9</t>
+          <t>BACK_SHALLOW:7-9:16</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -14142,12 +14142,12 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:16:9-11</t>
+          <t>BACK_SHALLOW:9-11:16</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -14194,12 +14194,12 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:16:11-13</t>
+          <t>BACK_SHALLOW:11-13:16</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -14246,12 +14246,12 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:16:13-15</t>
+          <t>BACK_SHALLOW:13-15:16</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -14298,12 +14298,12 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:16:15-17</t>
+          <t>BACK_SHALLOW:15-17:16</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
@@ -14350,12 +14350,12 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:16:17-19</t>
+          <t>BACK_SHALLOW:17-19:16</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:16:19-21</t>
+          <t>BACK_SHALLOW:19-21:16</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:16:21-23</t>
+          <t>BACK_SHALLOW:21-23:16</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -14506,12 +14506,12 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:16:23-25</t>
+          <t>BACK_SHALLOW:23-25:16</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
@@ -14558,12 +14558,12 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:16:25-27</t>
+          <t>BACK_SHALLOW:25-27:16</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -14610,12 +14610,12 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>BACK_SHALLOW:16:27-29</t>
+          <t>BACK_SHALLOW:27-29:16</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
@@ -14662,12 +14662,12 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:17:0-1</t>
+          <t>BACK_INTER:0-1:17</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -14714,12 +14714,12 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:17:1-2</t>
+          <t>BACK_INTER:1-2:17</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
@@ -14766,12 +14766,12 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:17:2-3</t>
+          <t>BACK_INTER:2-3:17</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:17:3-4</t>
+          <t>BACK_INTER:3-4:17</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
@@ -14870,12 +14870,12 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:17:4-5</t>
+          <t>BACK_INTER:4-5:17</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -14922,12 +14922,12 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:17:5-7</t>
+          <t>BACK_INTER:5-7:17</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -14974,12 +14974,12 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:17:7-9</t>
+          <t>BACK_INTER:7-9:17</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -15026,12 +15026,12 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:17:9-11</t>
+          <t>BACK_INTER:9-11:17</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
@@ -15078,12 +15078,12 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:17:11-13</t>
+          <t>BACK_INTER:11-13:17</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -15130,12 +15130,12 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:17:13-15</t>
+          <t>BACK_INTER:13-15:17</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -15182,12 +15182,12 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:17:15-17</t>
+          <t>BACK_INTER:15-17:17</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -15234,12 +15234,12 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:17:17-19</t>
+          <t>BACK_INTER:17-19:17</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
@@ -15286,12 +15286,12 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:17:19-21</t>
+          <t>BACK_INTER:19-21:17</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -15338,12 +15338,12 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:17:21-23</t>
+          <t>BACK_INTER:21-23:17</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
@@ -15390,12 +15390,12 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:17:23-25</t>
+          <t>BACK_INTER:23-25:17</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -15442,12 +15442,12 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:17:25-27</t>
+          <t>BACK_INTER:25-27:17</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
@@ -15494,12 +15494,12 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:17:27-29</t>
+          <t>BACK_INTER:27-29:17</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -15546,12 +15546,12 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:18:0-1</t>
+          <t>BACK_INTER:0-1:18</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
@@ -15598,12 +15598,12 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:18:1-2</t>
+          <t>BACK_INTER:1-2:18</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
@@ -15650,12 +15650,12 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:18:2-3</t>
+          <t>BACK_INTER:2-3:18</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
@@ -15702,12 +15702,12 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:18:3-4</t>
+          <t>BACK_INTER:3-4:18</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
@@ -15754,12 +15754,12 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:18:4-5</t>
+          <t>BACK_INTER:4-5:18</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
@@ -15806,12 +15806,12 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:18:5-7</t>
+          <t>BACK_INTER:5-7:18</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
@@ -15858,12 +15858,12 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:18:7-9</t>
+          <t>BACK_INTER:7-9:18</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
@@ -15910,12 +15910,12 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:18:9-11</t>
+          <t>BACK_INTER:9-11:18</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
@@ -15962,12 +15962,12 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:18:11-13</t>
+          <t>BACK_INTER:11-13:18</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
@@ -16014,12 +16014,12 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:18:13-15</t>
+          <t>BACK_INTER:13-15:18</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
@@ -16066,12 +16066,12 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:18:15-17</t>
+          <t>BACK_INTER:15-17:18</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:18:17-19</t>
+          <t>BACK_INTER:17-19:18</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
@@ -16170,12 +16170,12 @@
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:18:19-21</t>
+          <t>BACK_INTER:19-21:18</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:18:21-23</t>
+          <t>BACK_INTER:21-23:18</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:18:23-25</t>
+          <t>BACK_INTER:23-25:18</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:18:25-27</t>
+          <t>BACK_INTER:25-27:18</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
@@ -16378,12 +16378,12 @@
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:18:27-29</t>
+          <t>BACK_INTER:27-29:18</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
@@ -16430,12 +16430,12 @@
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:19:0-1</t>
+          <t>BACK_INTER:0-1:19</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
@@ -16482,12 +16482,12 @@
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:19:1-2</t>
+          <t>BACK_INTER:1-2:19</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
@@ -16534,12 +16534,12 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:19:2-3</t>
+          <t>BACK_INTER:2-3:19</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -16586,12 +16586,12 @@
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:19:3-4</t>
+          <t>BACK_INTER:3-4:19</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
@@ -16638,12 +16638,12 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:19:4-5</t>
+          <t>BACK_INTER:4-5:19</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
@@ -16690,12 +16690,12 @@
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:19:5-7</t>
+          <t>BACK_INTER:5-7:19</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
@@ -16742,12 +16742,12 @@
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:19:7-9</t>
+          <t>BACK_INTER:7-9:19</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
@@ -16794,12 +16794,12 @@
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:19:9-11</t>
+          <t>BACK_INTER:9-11:19</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
@@ -16846,12 +16846,12 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:19:11-13</t>
+          <t>BACK_INTER:11-13:19</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
@@ -16898,12 +16898,12 @@
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:19:13-15</t>
+          <t>BACK_INTER:13-15:19</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
@@ -16950,12 +16950,12 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:19:15-17</t>
+          <t>BACK_INTER:15-17:19</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
@@ -17002,12 +17002,12 @@
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:19:17-19</t>
+          <t>BACK_INTER:17-19:19</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
@@ -17054,12 +17054,12 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:19:19-21</t>
+          <t>BACK_INTER:19-21:19</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
@@ -17106,12 +17106,12 @@
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:19:21-23</t>
+          <t>BACK_INTER:21-23:19</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
@@ -17158,12 +17158,12 @@
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:19:23-25</t>
+          <t>BACK_INTER:23-25:19</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
@@ -17210,12 +17210,12 @@
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:19:25-27</t>
+          <t>BACK_INTER:25-27:19</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
@@ -17262,12 +17262,12 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:19:27-29</t>
+          <t>BACK_INTER:27-29:19</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
@@ -17314,12 +17314,12 @@
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:20:0-1</t>
+          <t>BACK_INTER:0-1:20</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
@@ -17366,12 +17366,12 @@
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:20:1-2</t>
+          <t>BACK_INTER:1-2:20</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
@@ -17418,12 +17418,12 @@
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:20:2-3</t>
+          <t>BACK_INTER:2-3:20</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
@@ -17470,12 +17470,12 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:20:3-4</t>
+          <t>BACK_INTER:3-4:20</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
@@ -17522,12 +17522,12 @@
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:20:4-5</t>
+          <t>BACK_INTER:4-5:20</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
@@ -17574,12 +17574,12 @@
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:20:5-7</t>
+          <t>BACK_INTER:5-7:20</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
@@ -17626,12 +17626,12 @@
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:20:7-9</t>
+          <t>BACK_INTER:7-9:20</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
@@ -17678,12 +17678,12 @@
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:20:9-11</t>
+          <t>BACK_INTER:9-11:20</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
@@ -17730,12 +17730,12 @@
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:20:11-13</t>
+          <t>BACK_INTER:11-13:20</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
@@ -17782,12 +17782,12 @@
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:20:13-15</t>
+          <t>BACK_INTER:13-15:20</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
@@ -17834,12 +17834,12 @@
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:20:15-17</t>
+          <t>BACK_INTER:15-17:20</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
@@ -17886,12 +17886,12 @@
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:20:17-19</t>
+          <t>BACK_INTER:17-19:20</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
@@ -17938,12 +17938,12 @@
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:20:19-21</t>
+          <t>BACK_INTER:19-21:20</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
@@ -17990,12 +17990,12 @@
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:20:21-23</t>
+          <t>BACK_INTER:21-23:20</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
@@ -18042,12 +18042,12 @@
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:20:23-25</t>
+          <t>BACK_INTER:23-25:20</t>
         </is>
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
@@ -18094,12 +18094,12 @@
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:20:25-27</t>
+          <t>BACK_INTER:25-27:20</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
@@ -18146,12 +18146,12 @@
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>BACK_INTER:20:27-29</t>
+          <t>BACK_INTER:27-29:20</t>
         </is>
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
@@ -18198,12 +18198,12 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:21:0-1</t>
+          <t>BACK_DEEP:0-1:21</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
@@ -18250,12 +18250,12 @@
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:21:1-2</t>
+          <t>BACK_DEEP:1-2:21</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
@@ -18302,12 +18302,12 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:21:2-3</t>
+          <t>BACK_DEEP:2-3:21</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
@@ -18354,12 +18354,12 @@
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:21:3-4</t>
+          <t>BACK_DEEP:3-4:21</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
@@ -18406,12 +18406,12 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:21:4-5</t>
+          <t>BACK_DEEP:4-5:21</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
@@ -18458,12 +18458,12 @@
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:21:5-7</t>
+          <t>BACK_DEEP:5-7:21</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
@@ -18510,12 +18510,12 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:21:7-9</t>
+          <t>BACK_DEEP:7-9:21</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
@@ -18562,12 +18562,12 @@
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:21:9-11</t>
+          <t>BACK_DEEP:9-11:21</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
@@ -18614,12 +18614,12 @@
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:21:11-13</t>
+          <t>BACK_DEEP:11-13:21</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
@@ -18666,12 +18666,12 @@
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:21:13-15</t>
+          <t>BACK_DEEP:13-15:21</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
@@ -18718,12 +18718,12 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:21:15-17</t>
+          <t>BACK_DEEP:15-17:21</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
@@ -18770,12 +18770,12 @@
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:21:17-19</t>
+          <t>BACK_DEEP:17-19:21</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
@@ -18822,12 +18822,12 @@
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:21:19-21</t>
+          <t>BACK_DEEP:19-21:21</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
@@ -18874,12 +18874,12 @@
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:21:21-23</t>
+          <t>BACK_DEEP:21-23:21</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
@@ -18926,12 +18926,12 @@
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:21:23-25</t>
+          <t>BACK_DEEP:23-25:21</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
@@ -18978,12 +18978,12 @@
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:21:25-27</t>
+          <t>BACK_DEEP:25-27:21</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
@@ -19030,12 +19030,12 @@
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:21:27-29</t>
+          <t>BACK_DEEP:27-29:21</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
@@ -19082,12 +19082,12 @@
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:22:0-1</t>
+          <t>BACK_DEEP:0-1:22</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:22:1-2</t>
+          <t>BACK_DEEP:1-2:22</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
@@ -19186,12 +19186,12 @@
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:22:2-3</t>
+          <t>BACK_DEEP:2-3:22</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
@@ -19238,12 +19238,12 @@
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:22:3-4</t>
+          <t>BACK_DEEP:3-4:22</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
@@ -19290,12 +19290,12 @@
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:22:4-5</t>
+          <t>BACK_DEEP:4-5:22</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
@@ -19342,12 +19342,12 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:22:5-7</t>
+          <t>BACK_DEEP:5-7:22</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
@@ -19394,12 +19394,12 @@
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:22:7-9</t>
+          <t>BACK_DEEP:7-9:22</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
@@ -19446,12 +19446,12 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:22:9-11</t>
+          <t>BACK_DEEP:9-11:22</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
@@ -19498,12 +19498,12 @@
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:22:11-13</t>
+          <t>BACK_DEEP:11-13:22</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
@@ -19550,12 +19550,12 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:22:13-15</t>
+          <t>BACK_DEEP:13-15:22</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
@@ -19602,12 +19602,12 @@
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:22:15-17</t>
+          <t>BACK_DEEP:15-17:22</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
@@ -19654,12 +19654,12 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:22:17-19</t>
+          <t>BACK_DEEP:17-19:22</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
@@ -19706,12 +19706,12 @@
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:22:19-21</t>
+          <t>BACK_DEEP:19-21:22</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
@@ -19758,12 +19758,12 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:22:21-23</t>
+          <t>BACK_DEEP:21-23:22</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
@@ -19810,12 +19810,12 @@
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:22:23-25</t>
+          <t>BACK_DEEP:23-25:22</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
@@ -19862,12 +19862,12 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:22:25-27</t>
+          <t>BACK_DEEP:25-27:22</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
@@ -19914,12 +19914,12 @@
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:22:27-29</t>
+          <t>BACK_DEEP:27-29:22</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
@@ -19966,12 +19966,12 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:23:0-1</t>
+          <t>BACK_DEEP:0-1:23</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
@@ -20018,12 +20018,12 @@
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:23:1-2</t>
+          <t>BACK_DEEP:1-2:23</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
@@ -20070,12 +20070,12 @@
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:23:2-3</t>
+          <t>BACK_DEEP:2-3:23</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:23:3-4</t>
+          <t>BACK_DEEP:3-4:23</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
@@ -20174,12 +20174,12 @@
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:23:4-5</t>
+          <t>BACK_DEEP:4-5:23</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
@@ -20226,12 +20226,12 @@
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:23:5-7</t>
+          <t>BACK_DEEP:5-7:23</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
@@ -20278,12 +20278,12 @@
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:23:7-9</t>
+          <t>BACK_DEEP:7-9:23</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
@@ -20330,12 +20330,12 @@
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:23:9-11</t>
+          <t>BACK_DEEP:9-11:23</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
@@ -20382,12 +20382,12 @@
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:23:11-13</t>
+          <t>BACK_DEEP:11-13:23</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
@@ -20434,12 +20434,12 @@
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:23:13-15</t>
+          <t>BACK_DEEP:13-15:23</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
@@ -20486,12 +20486,12 @@
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:23:15-17</t>
+          <t>BACK_DEEP:15-17:23</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
@@ -20538,12 +20538,12 @@
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:23:17-19</t>
+          <t>BACK_DEEP:17-19:23</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
@@ -20590,12 +20590,12 @@
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:23:19-21</t>
+          <t>BACK_DEEP:19-21:23</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
@@ -20642,12 +20642,12 @@
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:23:21-23</t>
+          <t>BACK_DEEP:21-23:23</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
@@ -20694,12 +20694,12 @@
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:23:23-25</t>
+          <t>BACK_DEEP:23-25:23</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
@@ -20746,12 +20746,12 @@
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:23:25-27</t>
+          <t>BACK_DEEP:25-27:23</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
@@ -20798,12 +20798,12 @@
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:23:27-29</t>
+          <t>BACK_DEEP:27-29:23</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
@@ -20850,12 +20850,12 @@
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:24:0-1</t>
+          <t>BACK_DEEP:0-1:24</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
@@ -20902,12 +20902,12 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:24:1-2</t>
+          <t>BACK_DEEP:1-2:24</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
@@ -20954,12 +20954,12 @@
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:24:2-3</t>
+          <t>BACK_DEEP:2-3:24</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
@@ -21006,12 +21006,12 @@
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:24:3-4</t>
+          <t>BACK_DEEP:3-4:24</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
@@ -21058,12 +21058,12 @@
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:24:4-5</t>
+          <t>BACK_DEEP:4-5:24</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
@@ -21110,12 +21110,12 @@
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:24:5-7</t>
+          <t>BACK_DEEP:5-7:24</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
@@ -21162,12 +21162,12 @@
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:24:7-9</t>
+          <t>BACK_DEEP:7-9:24</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
@@ -21214,12 +21214,12 @@
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:24:9-11</t>
+          <t>BACK_DEEP:9-11:24</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
@@ -21266,12 +21266,12 @@
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:24:11-13</t>
+          <t>BACK_DEEP:11-13:24</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
@@ -21318,12 +21318,12 @@
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:24:13-15</t>
+          <t>BACK_DEEP:13-15:24</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
@@ -21370,12 +21370,12 @@
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:24:15-17</t>
+          <t>BACK_DEEP:15-17:24</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
@@ -21422,12 +21422,12 @@
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:24:17-19</t>
+          <t>BACK_DEEP:17-19:24</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
@@ -21474,12 +21474,12 @@
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:24:19-21</t>
+          <t>BACK_DEEP:19-21:24</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
@@ -21526,12 +21526,12 @@
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:24:21-23</t>
+          <t>BACK_DEEP:21-23:24</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
@@ -21578,12 +21578,12 @@
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:24:23-25</t>
+          <t>BACK_DEEP:23-25:24</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:24:25-27</t>
+          <t>BACK_DEEP:25-27:24</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
@@ -21682,12 +21682,12 @@
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>BACK_DEEP:24:27-29</t>
+          <t>BACK_DEEP:27-29:24</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
@@ -21734,12 +21734,12 @@
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:25:0-1</t>
+          <t>MID_SHALLOW:0-1:25</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
@@ -21786,12 +21786,12 @@
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:25:1-2</t>
+          <t>MID_SHALLOW:1-2:25</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
@@ -21838,12 +21838,12 @@
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:25:2-3</t>
+          <t>MID_SHALLOW:2-3:25</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
@@ -21890,12 +21890,12 @@
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:25:3-4</t>
+          <t>MID_SHALLOW:3-4:25</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
@@ -21942,12 +21942,12 @@
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:25:4-5</t>
+          <t>MID_SHALLOW:4-5:25</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
@@ -21994,12 +21994,12 @@
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:25:5-7</t>
+          <t>MID_SHALLOW:5-7:25</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
@@ -22046,12 +22046,12 @@
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:25:7-9</t>
+          <t>MID_SHALLOW:7-9:25</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
@@ -22098,12 +22098,12 @@
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:25:9-11</t>
+          <t>MID_SHALLOW:9-11:25</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
@@ -22150,12 +22150,12 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:25:11-13</t>
+          <t>MID_SHALLOW:11-13:25</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
@@ -22202,12 +22202,12 @@
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:25:13-15</t>
+          <t>MID_SHALLOW:13-15:25</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
@@ -22254,12 +22254,12 @@
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:25:15-17</t>
+          <t>MID_SHALLOW:15-17:25</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
@@ -22306,12 +22306,12 @@
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:25:17-19</t>
+          <t>MID_SHALLOW:17-19:25</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
@@ -22358,12 +22358,12 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:25:19-21</t>
+          <t>MID_SHALLOW:19-21:25</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:25:21-23</t>
+          <t>MID_SHALLOW:21-23:25</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
@@ -22462,12 +22462,12 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:25:23-25</t>
+          <t>MID_SHALLOW:23-25:25</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
@@ -22514,12 +22514,12 @@
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:25:25-27</t>
+          <t>MID_SHALLOW:25-27:25</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
@@ -22566,12 +22566,12 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:25:27-29</t>
+          <t>MID_SHALLOW:27-29:25</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
@@ -22618,12 +22618,12 @@
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:26:0-1</t>
+          <t>MID_SHALLOW:0-1:26</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
@@ -22670,12 +22670,12 @@
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:26:1-2</t>
+          <t>MID_SHALLOW:1-2:26</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
@@ -22722,12 +22722,12 @@
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:26:2-3</t>
+          <t>MID_SHALLOW:2-3:26</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
@@ -22774,12 +22774,12 @@
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:26:3-4</t>
+          <t>MID_SHALLOW:3-4:26</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
@@ -22826,12 +22826,12 @@
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:26:4-5</t>
+          <t>MID_SHALLOW:4-5:26</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
@@ -22878,12 +22878,12 @@
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:26:5-7</t>
+          <t>MID_SHALLOW:5-7:26</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
@@ -22930,12 +22930,12 @@
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:26:7-9</t>
+          <t>MID_SHALLOW:7-9:26</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr">
@@ -22982,12 +22982,12 @@
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:26:9-11</t>
+          <t>MID_SHALLOW:9-11:26</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr">
@@ -23034,12 +23034,12 @@
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:26:11-13</t>
+          <t>MID_SHALLOW:11-13:26</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr">
@@ -23086,12 +23086,12 @@
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:26:13-15</t>
+          <t>MID_SHALLOW:13-15:26</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr">
@@ -23138,12 +23138,12 @@
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:26:15-17</t>
+          <t>MID_SHALLOW:15-17:26</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr">
@@ -23190,12 +23190,12 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:26:17-19</t>
+          <t>MID_SHALLOW:17-19:26</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr">
@@ -23242,12 +23242,12 @@
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:26:19-21</t>
+          <t>MID_SHALLOW:19-21:26</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
@@ -23294,12 +23294,12 @@
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:26:21-23</t>
+          <t>MID_SHALLOW:21-23:26</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr">
@@ -23346,12 +23346,12 @@
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:26:23-25</t>
+          <t>MID_SHALLOW:23-25:26</t>
         </is>
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr">
@@ -23398,12 +23398,12 @@
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:26:25-27</t>
+          <t>MID_SHALLOW:25-27:26</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr">
@@ -23450,12 +23450,12 @@
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:26:27-29</t>
+          <t>MID_SHALLOW:27-29:26</t>
         </is>
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr">
@@ -23502,12 +23502,12 @@
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:27:0-1</t>
+          <t>MID_SHALLOW:0-1:27</t>
         </is>
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr">
@@ -23554,12 +23554,12 @@
       </c>
       <c r="C445" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:27:1-2</t>
+          <t>MID_SHALLOW:1-2:27</t>
         </is>
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr">
@@ -23606,12 +23606,12 @@
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:27:2-3</t>
+          <t>MID_SHALLOW:2-3:27</t>
         </is>
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr">
@@ -23658,12 +23658,12 @@
       </c>
       <c r="C447" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:27:3-4</t>
+          <t>MID_SHALLOW:3-4:27</t>
         </is>
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E447" s="2" t="inlineStr">
@@ -23710,12 +23710,12 @@
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:27:4-5</t>
+          <t>MID_SHALLOW:4-5:27</t>
         </is>
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr">
@@ -23762,12 +23762,12 @@
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:27:5-7</t>
+          <t>MID_SHALLOW:5-7:27</t>
         </is>
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr">
@@ -23814,12 +23814,12 @@
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:27:7-9</t>
+          <t>MID_SHALLOW:7-9:27</t>
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr">
@@ -23866,12 +23866,12 @@
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:27:9-11</t>
+          <t>MID_SHALLOW:9-11:27</t>
         </is>
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr">
@@ -23918,12 +23918,12 @@
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:27:11-13</t>
+          <t>MID_SHALLOW:11-13:27</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E452" s="2" t="inlineStr">
@@ -23970,12 +23970,12 @@
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:27:13-15</t>
+          <t>MID_SHALLOW:13-15:27</t>
         </is>
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr">
@@ -24022,12 +24022,12 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:27:15-17</t>
+          <t>MID_SHALLOW:15-17:27</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr">
@@ -24074,12 +24074,12 @@
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:27:17-19</t>
+          <t>MID_SHALLOW:17-19:27</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E455" s="2" t="inlineStr">
@@ -24126,12 +24126,12 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:27:19-21</t>
+          <t>MID_SHALLOW:19-21:27</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr">
@@ -24178,12 +24178,12 @@
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:27:21-23</t>
+          <t>MID_SHALLOW:21-23:27</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr">
@@ -24230,12 +24230,12 @@
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:27:23-25</t>
+          <t>MID_SHALLOW:23-25:27</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
@@ -24282,12 +24282,12 @@
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:27:25-27</t>
+          <t>MID_SHALLOW:25-27:27</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
@@ -24334,12 +24334,12 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:27:27-29</t>
+          <t>MID_SHALLOW:27-29:27</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
@@ -24386,12 +24386,12 @@
       </c>
       <c r="C461" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:28:0-1</t>
+          <t>MID_SHALLOW:0-1:28</t>
         </is>
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr">
@@ -24438,12 +24438,12 @@
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:28:1-2</t>
+          <t>MID_SHALLOW:1-2:28</t>
         </is>
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
@@ -24490,12 +24490,12 @@
       </c>
       <c r="C463" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:28:2-3</t>
+          <t>MID_SHALLOW:2-3:28</t>
         </is>
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E463" s="2" t="inlineStr">
@@ -24542,12 +24542,12 @@
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:28:3-4</t>
+          <t>MID_SHALLOW:3-4:28</t>
         </is>
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
@@ -24594,12 +24594,12 @@
       </c>
       <c r="C465" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:28:4-5</t>
+          <t>MID_SHALLOW:4-5:28</t>
         </is>
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr">
@@ -24646,12 +24646,12 @@
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:28:5-7</t>
+          <t>MID_SHALLOW:5-7:28</t>
         </is>
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
@@ -24698,12 +24698,12 @@
       </c>
       <c r="C467" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:28:7-9</t>
+          <t>MID_SHALLOW:7-9:28</t>
         </is>
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr">
@@ -24750,12 +24750,12 @@
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:28:9-11</t>
+          <t>MID_SHALLOW:9-11:28</t>
         </is>
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
@@ -24802,12 +24802,12 @@
       </c>
       <c r="C469" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:28:11-13</t>
+          <t>MID_SHALLOW:11-13:28</t>
         </is>
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
@@ -24854,12 +24854,12 @@
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:28:13-15</t>
+          <t>MID_SHALLOW:13-15:28</t>
         </is>
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
@@ -24906,12 +24906,12 @@
       </c>
       <c r="C471" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:28:15-17</t>
+          <t>MID_SHALLOW:15-17:28</t>
         </is>
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
@@ -24958,12 +24958,12 @@
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:28:17-19</t>
+          <t>MID_SHALLOW:17-19:28</t>
         </is>
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
@@ -25010,12 +25010,12 @@
       </c>
       <c r="C473" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:28:19-21</t>
+          <t>MID_SHALLOW:19-21:28</t>
         </is>
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
@@ -25062,12 +25062,12 @@
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:28:21-23</t>
+          <t>MID_SHALLOW:21-23:28</t>
         </is>
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
@@ -25114,12 +25114,12 @@
       </c>
       <c r="C475" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:28:23-25</t>
+          <t>MID_SHALLOW:23-25:28</t>
         </is>
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr">
@@ -25166,12 +25166,12 @@
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:28:25-27</t>
+          <t>MID_SHALLOW:25-27:28</t>
         </is>
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
@@ -25218,12 +25218,12 @@
       </c>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>MID_SHALLOW:28:27-29</t>
+          <t>MID_SHALLOW:27-29:28</t>
         </is>
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr">
@@ -25270,12 +25270,12 @@
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:29:0-1</t>
+          <t>MID_INTER:0-1:29</t>
         </is>
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr">
@@ -25322,12 +25322,12 @@
       </c>
       <c r="C479" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:29:1-2</t>
+          <t>MID_INTER:1-2:29</t>
         </is>
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
@@ -25374,12 +25374,12 @@
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:29:2-3</t>
+          <t>MID_INTER:2-3:29</t>
         </is>
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
@@ -25426,12 +25426,12 @@
       </c>
       <c r="C481" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:29:3-4</t>
+          <t>MID_INTER:3-4:29</t>
         </is>
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr">
@@ -25478,12 +25478,12 @@
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:29:4-5</t>
+          <t>MID_INTER:4-5:29</t>
         </is>
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
@@ -25530,12 +25530,12 @@
       </c>
       <c r="C483" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:29:5-7</t>
+          <t>MID_INTER:5-7:29</t>
         </is>
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E483" s="2" t="inlineStr">
@@ -25582,12 +25582,12 @@
       </c>
       <c r="C484" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:29:7-9</t>
+          <t>MID_INTER:7-9:29</t>
         </is>
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr">
@@ -25634,12 +25634,12 @@
       </c>
       <c r="C485" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:29:9-11</t>
+          <t>MID_INTER:9-11:29</t>
         </is>
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr">
@@ -25686,12 +25686,12 @@
       </c>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:29:11-13</t>
+          <t>MID_INTER:11-13:29</t>
         </is>
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr">
@@ -25738,12 +25738,12 @@
       </c>
       <c r="C487" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:29:13-15</t>
+          <t>MID_INTER:13-15:29</t>
         </is>
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr">
@@ -25790,12 +25790,12 @@
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:29:15-17</t>
+          <t>MID_INTER:15-17:29</t>
         </is>
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
@@ -25842,12 +25842,12 @@
       </c>
       <c r="C489" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:29:17-19</t>
+          <t>MID_INTER:17-19:29</t>
         </is>
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr">
@@ -25894,12 +25894,12 @@
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:29:19-21</t>
+          <t>MID_INTER:19-21:29</t>
         </is>
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr">
@@ -25946,12 +25946,12 @@
       </c>
       <c r="C491" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:29:21-23</t>
+          <t>MID_INTER:21-23:29</t>
         </is>
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr">
@@ -25998,12 +25998,12 @@
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:29:23-25</t>
+          <t>MID_INTER:23-25:29</t>
         </is>
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E492" s="2" t="inlineStr">
@@ -26050,12 +26050,12 @@
       </c>
       <c r="C493" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:29:25-27</t>
+          <t>MID_INTER:25-27:29</t>
         </is>
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr">
@@ -26102,12 +26102,12 @@
       </c>
       <c r="C494" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:29:27-29</t>
+          <t>MID_INTER:27-29:29</t>
         </is>
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E494" s="2" t="inlineStr">
@@ -26154,12 +26154,12 @@
       </c>
       <c r="C495" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:30:0-1</t>
+          <t>MID_INTER:0-1:30</t>
         </is>
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr">
@@ -26206,12 +26206,12 @@
       </c>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:30:1-2</t>
+          <t>MID_INTER:1-2:30</t>
         </is>
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr">
@@ -26258,12 +26258,12 @@
       </c>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:30:2-3</t>
+          <t>MID_INTER:2-3:30</t>
         </is>
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr">
@@ -26310,12 +26310,12 @@
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:30:3-4</t>
+          <t>MID_INTER:3-4:30</t>
         </is>
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
@@ -26362,12 +26362,12 @@
       </c>
       <c r="C499" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:30:4-5</t>
+          <t>MID_INTER:4-5:30</t>
         </is>
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
@@ -26414,12 +26414,12 @@
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:30:5-7</t>
+          <t>MID_INTER:5-7:30</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr">
@@ -26466,12 +26466,12 @@
       </c>
       <c r="C501" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:30:7-9</t>
+          <t>MID_INTER:7-9:30</t>
         </is>
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E501" s="2" t="inlineStr">
@@ -26518,12 +26518,12 @@
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:30:9-11</t>
+          <t>MID_INTER:9-11:30</t>
         </is>
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="C503" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:30:11-13</t>
+          <t>MID_INTER:11-13:30</t>
         </is>
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E503" s="2" t="inlineStr">
@@ -26622,12 +26622,12 @@
       </c>
       <c r="C504" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:30:13-15</t>
+          <t>MID_INTER:13-15:30</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr">
@@ -26674,12 +26674,12 @@
       </c>
       <c r="C505" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:30:15-17</t>
+          <t>MID_INTER:15-17:30</t>
         </is>
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E505" s="2" t="inlineStr">
@@ -26726,12 +26726,12 @@
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:30:17-19</t>
+          <t>MID_INTER:17-19:30</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
@@ -26778,12 +26778,12 @@
       </c>
       <c r="C507" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:30:19-21</t>
+          <t>MID_INTER:19-21:30</t>
         </is>
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E507" s="2" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:30:21-23</t>
+          <t>MID_INTER:21-23:30</t>
         </is>
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr">
@@ -26882,12 +26882,12 @@
       </c>
       <c r="C509" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:30:23-25</t>
+          <t>MID_INTER:23-25:30</t>
         </is>
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E509" s="2" t="inlineStr">
@@ -26934,12 +26934,12 @@
       </c>
       <c r="C510" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:30:25-27</t>
+          <t>MID_INTER:25-27:30</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E510" s="2" t="inlineStr">
@@ -26986,12 +26986,12 @@
       </c>
       <c r="C511" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:30:27-29</t>
+          <t>MID_INTER:27-29:30</t>
         </is>
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr">
@@ -27038,12 +27038,12 @@
       </c>
       <c r="C512" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:31:0-1</t>
+          <t>MID_INTER:0-1:31</t>
         </is>
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr">
@@ -27090,12 +27090,12 @@
       </c>
       <c r="C513" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:31:1-2</t>
+          <t>MID_INTER:1-2:31</t>
         </is>
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E513" s="2" t="inlineStr">
@@ -27142,12 +27142,12 @@
       </c>
       <c r="C514" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:31:2-3</t>
+          <t>MID_INTER:2-3:31</t>
         </is>
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E514" s="2" t="inlineStr">
@@ -27194,12 +27194,12 @@
       </c>
       <c r="C515" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:31:3-4</t>
+          <t>MID_INTER:3-4:31</t>
         </is>
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E515" s="2" t="inlineStr">
@@ -27246,12 +27246,12 @@
       </c>
       <c r="C516" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:31:4-5</t>
+          <t>MID_INTER:4-5:31</t>
         </is>
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr">
@@ -27298,12 +27298,12 @@
       </c>
       <c r="C517" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:31:5-7</t>
+          <t>MID_INTER:5-7:31</t>
         </is>
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E517" s="2" t="inlineStr">
@@ -27350,12 +27350,12 @@
       </c>
       <c r="C518" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:31:7-9</t>
+          <t>MID_INTER:7-9:31</t>
         </is>
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E518" s="2" t="inlineStr">
@@ -27402,12 +27402,12 @@
       </c>
       <c r="C519" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:31:9-11</t>
+          <t>MID_INTER:9-11:31</t>
         </is>
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E519" s="2" t="inlineStr">
@@ -27454,12 +27454,12 @@
       </c>
       <c r="C520" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:31:11-13</t>
+          <t>MID_INTER:11-13:31</t>
         </is>
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E520" s="2" t="inlineStr">
@@ -27506,12 +27506,12 @@
       </c>
       <c r="C521" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:31:13-15</t>
+          <t>MID_INTER:13-15:31</t>
         </is>
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E521" s="2" t="inlineStr">
@@ -27558,12 +27558,12 @@
       </c>
       <c r="C522" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:31:15-17</t>
+          <t>MID_INTER:15-17:31</t>
         </is>
       </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E522" s="2" t="inlineStr">
@@ -27610,12 +27610,12 @@
       </c>
       <c r="C523" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:31:17-19</t>
+          <t>MID_INTER:17-19:31</t>
         </is>
       </c>
       <c r="D523" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E523" s="2" t="inlineStr">
@@ -27662,12 +27662,12 @@
       </c>
       <c r="C524" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:31:19-21</t>
+          <t>MID_INTER:19-21:31</t>
         </is>
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E524" s="2" t="inlineStr">
@@ -27714,12 +27714,12 @@
       </c>
       <c r="C525" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:31:21-23</t>
+          <t>MID_INTER:21-23:31</t>
         </is>
       </c>
       <c r="D525" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E525" s="2" t="inlineStr">
@@ -27766,12 +27766,12 @@
       </c>
       <c r="C526" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:31:23-25</t>
+          <t>MID_INTER:23-25:31</t>
         </is>
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E526" s="2" t="inlineStr">
@@ -27818,12 +27818,12 @@
       </c>
       <c r="C527" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:31:25-27</t>
+          <t>MID_INTER:25-27:31</t>
         </is>
       </c>
       <c r="D527" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E527" s="2" t="inlineStr">
@@ -27870,12 +27870,12 @@
       </c>
       <c r="C528" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:31:27-29</t>
+          <t>MID_INTER:27-29:31</t>
         </is>
       </c>
       <c r="D528" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E528" s="2" t="inlineStr">
@@ -27922,12 +27922,12 @@
       </c>
       <c r="C529" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:32:0-1</t>
+          <t>MID_INTER:0-1:32</t>
         </is>
       </c>
       <c r="D529" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E529" s="2" t="inlineStr">
@@ -27974,12 +27974,12 @@
       </c>
       <c r="C530" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:32:1-2</t>
+          <t>MID_INTER:1-2:32</t>
         </is>
       </c>
       <c r="D530" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E530" s="2" t="inlineStr">
@@ -28026,12 +28026,12 @@
       </c>
       <c r="C531" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:32:2-3</t>
+          <t>MID_INTER:2-3:32</t>
         </is>
       </c>
       <c r="D531" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E531" s="2" t="inlineStr">
@@ -28078,12 +28078,12 @@
       </c>
       <c r="C532" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:32:3-4</t>
+          <t>MID_INTER:3-4:32</t>
         </is>
       </c>
       <c r="D532" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E532" s="2" t="inlineStr">
@@ -28130,12 +28130,12 @@
       </c>
       <c r="C533" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:32:4-5</t>
+          <t>MID_INTER:4-5:32</t>
         </is>
       </c>
       <c r="D533" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E533" s="2" t="inlineStr">
@@ -28182,12 +28182,12 @@
       </c>
       <c r="C534" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:32:5-7</t>
+          <t>MID_INTER:5-7:32</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E534" s="2" t="inlineStr">
@@ -28234,12 +28234,12 @@
       </c>
       <c r="C535" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:32:7-9</t>
+          <t>MID_INTER:7-9:32</t>
         </is>
       </c>
       <c r="D535" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E535" s="2" t="inlineStr">
@@ -28286,12 +28286,12 @@
       </c>
       <c r="C536" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:32:9-11</t>
+          <t>MID_INTER:9-11:32</t>
         </is>
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E536" s="2" t="inlineStr">
@@ -28338,12 +28338,12 @@
       </c>
       <c r="C537" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:32:11-13</t>
+          <t>MID_INTER:11-13:32</t>
         </is>
       </c>
       <c r="D537" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E537" s="2" t="inlineStr">
@@ -28390,12 +28390,12 @@
       </c>
       <c r="C538" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:32:13-15</t>
+          <t>MID_INTER:13-15:32</t>
         </is>
       </c>
       <c r="D538" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E538" s="2" t="inlineStr">
@@ -28442,12 +28442,12 @@
       </c>
       <c r="C539" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:32:15-17</t>
+          <t>MID_INTER:15-17:32</t>
         </is>
       </c>
       <c r="D539" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E539" s="2" t="inlineStr">
@@ -28494,12 +28494,12 @@
       </c>
       <c r="C540" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:32:17-19</t>
+          <t>MID_INTER:17-19:32</t>
         </is>
       </c>
       <c r="D540" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E540" s="2" t="inlineStr">
@@ -28546,12 +28546,12 @@
       </c>
       <c r="C541" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:32:19-21</t>
+          <t>MID_INTER:19-21:32</t>
         </is>
       </c>
       <c r="D541" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E541" s="2" t="inlineStr">
@@ -28598,12 +28598,12 @@
       </c>
       <c r="C542" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:32:21-23</t>
+          <t>MID_INTER:21-23:32</t>
         </is>
       </c>
       <c r="D542" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E542" s="2" t="inlineStr">
@@ -28650,12 +28650,12 @@
       </c>
       <c r="C543" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:32:23-25</t>
+          <t>MID_INTER:23-25:32</t>
         </is>
       </c>
       <c r="D543" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E543" s="2" t="inlineStr">
@@ -28702,12 +28702,12 @@
       </c>
       <c r="C544" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:32:25-27</t>
+          <t>MID_INTER:25-27:32</t>
         </is>
       </c>
       <c r="D544" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E544" s="2" t="inlineStr">
@@ -28754,12 +28754,12 @@
       </c>
       <c r="C545" s="2" t="inlineStr">
         <is>
-          <t>MID_INTER:32:27-29</t>
+          <t>MID_INTER:27-29:32</t>
         </is>
       </c>
       <c r="D545" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E545" s="2" t="inlineStr">
@@ -28806,12 +28806,12 @@
       </c>
       <c r="C546" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:33:0-1</t>
+          <t>MID_DEEP:0-1:33</t>
         </is>
       </c>
       <c r="D546" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E546" s="2" t="inlineStr">
@@ -28858,12 +28858,12 @@
       </c>
       <c r="C547" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:33:1-2</t>
+          <t>MID_DEEP:1-2:33</t>
         </is>
       </c>
       <c r="D547" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E547" s="2" t="inlineStr">
@@ -28910,12 +28910,12 @@
       </c>
       <c r="C548" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:33:2-3</t>
+          <t>MID_DEEP:2-3:33</t>
         </is>
       </c>
       <c r="D548" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E548" s="2" t="inlineStr">
@@ -28962,12 +28962,12 @@
       </c>
       <c r="C549" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:33:3-4</t>
+          <t>MID_DEEP:3-4:33</t>
         </is>
       </c>
       <c r="D549" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E549" s="2" t="inlineStr">
@@ -29014,12 +29014,12 @@
       </c>
       <c r="C550" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:33:4-5</t>
+          <t>MID_DEEP:4-5:33</t>
         </is>
       </c>
       <c r="D550" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E550" s="2" t="inlineStr">
@@ -29066,12 +29066,12 @@
       </c>
       <c r="C551" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:33:5-7</t>
+          <t>MID_DEEP:5-7:33</t>
         </is>
       </c>
       <c r="D551" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E551" s="2" t="inlineStr">
@@ -29118,12 +29118,12 @@
       </c>
       <c r="C552" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:33:7-9</t>
+          <t>MID_DEEP:7-9:33</t>
         </is>
       </c>
       <c r="D552" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E552" s="2" t="inlineStr">
@@ -29170,12 +29170,12 @@
       </c>
       <c r="C553" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:33:9-11</t>
+          <t>MID_DEEP:9-11:33</t>
         </is>
       </c>
       <c r="D553" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E553" s="2" t="inlineStr">
@@ -29222,12 +29222,12 @@
       </c>
       <c r="C554" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:33:11-13</t>
+          <t>MID_DEEP:11-13:33</t>
         </is>
       </c>
       <c r="D554" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E554" s="2" t="inlineStr">
@@ -29274,12 +29274,12 @@
       </c>
       <c r="C555" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:33:13-15</t>
+          <t>MID_DEEP:13-15:33</t>
         </is>
       </c>
       <c r="D555" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E555" s="2" t="inlineStr">
@@ -29326,12 +29326,12 @@
       </c>
       <c r="C556" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:33:15-17</t>
+          <t>MID_DEEP:15-17:33</t>
         </is>
       </c>
       <c r="D556" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E556" s="2" t="inlineStr">
@@ -29378,12 +29378,12 @@
       </c>
       <c r="C557" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:33:17-19</t>
+          <t>MID_DEEP:17-19:33</t>
         </is>
       </c>
       <c r="D557" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E557" s="2" t="inlineStr">
@@ -29430,12 +29430,12 @@
       </c>
       <c r="C558" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:33:19-21</t>
+          <t>MID_DEEP:19-21:33</t>
         </is>
       </c>
       <c r="D558" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E558" s="2" t="inlineStr">
@@ -29482,12 +29482,12 @@
       </c>
       <c r="C559" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:33:21-23</t>
+          <t>MID_DEEP:21-23:33</t>
         </is>
       </c>
       <c r="D559" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E559" s="2" t="inlineStr">
@@ -29534,12 +29534,12 @@
       </c>
       <c r="C560" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:33:23-25</t>
+          <t>MID_DEEP:23-25:33</t>
         </is>
       </c>
       <c r="D560" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E560" s="2" t="inlineStr">
@@ -29586,12 +29586,12 @@
       </c>
       <c r="C561" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:33:25-27</t>
+          <t>MID_DEEP:25-27:33</t>
         </is>
       </c>
       <c r="D561" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E561" s="2" t="inlineStr">
@@ -29638,12 +29638,12 @@
       </c>
       <c r="C562" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:33:27-29</t>
+          <t>MID_DEEP:27-29:33</t>
         </is>
       </c>
       <c r="D562" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E562" s="2" t="inlineStr">
@@ -29690,12 +29690,12 @@
       </c>
       <c r="C563" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:34:0-1</t>
+          <t>MID_DEEP:0-1:34</t>
         </is>
       </c>
       <c r="D563" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E563" s="2" t="inlineStr">
@@ -29742,12 +29742,12 @@
       </c>
       <c r="C564" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:34:1-2</t>
+          <t>MID_DEEP:1-2:34</t>
         </is>
       </c>
       <c r="D564" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E564" s="2" t="inlineStr">
@@ -29794,12 +29794,12 @@
       </c>
       <c r="C565" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:34:2-3</t>
+          <t>MID_DEEP:2-3:34</t>
         </is>
       </c>
       <c r="D565" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E565" s="2" t="inlineStr">
@@ -29846,12 +29846,12 @@
       </c>
       <c r="C566" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:34:3-4</t>
+          <t>MID_DEEP:3-4:34</t>
         </is>
       </c>
       <c r="D566" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E566" s="2" t="inlineStr">
@@ -29898,12 +29898,12 @@
       </c>
       <c r="C567" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:34:4-5</t>
+          <t>MID_DEEP:4-5:34</t>
         </is>
       </c>
       <c r="D567" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E567" s="2" t="inlineStr">
@@ -29950,12 +29950,12 @@
       </c>
       <c r="C568" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:34:5-7</t>
+          <t>MID_DEEP:5-7:34</t>
         </is>
       </c>
       <c r="D568" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E568" s="2" t="inlineStr">
@@ -30002,12 +30002,12 @@
       </c>
       <c r="C569" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:34:7-9</t>
+          <t>MID_DEEP:7-9:34</t>
         </is>
       </c>
       <c r="D569" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E569" s="2" t="inlineStr">
@@ -30054,12 +30054,12 @@
       </c>
       <c r="C570" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:34:9-11</t>
+          <t>MID_DEEP:9-11:34</t>
         </is>
       </c>
       <c r="D570" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E570" s="2" t="inlineStr">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="C571" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:34:11-13</t>
+          <t>MID_DEEP:11-13:34</t>
         </is>
       </c>
       <c r="D571" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E571" s="2" t="inlineStr">
@@ -30158,12 +30158,12 @@
       </c>
       <c r="C572" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:34:13-15</t>
+          <t>MID_DEEP:13-15:34</t>
         </is>
       </c>
       <c r="D572" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E572" s="2" t="inlineStr">
@@ -30210,12 +30210,12 @@
       </c>
       <c r="C573" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:34:15-17</t>
+          <t>MID_DEEP:15-17:34</t>
         </is>
       </c>
       <c r="D573" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E573" s="2" t="inlineStr">
@@ -30262,12 +30262,12 @@
       </c>
       <c r="C574" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:34:17-19</t>
+          <t>MID_DEEP:17-19:34</t>
         </is>
       </c>
       <c r="D574" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E574" s="2" t="inlineStr">
@@ -30314,12 +30314,12 @@
       </c>
       <c r="C575" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:34:19-21</t>
+          <t>MID_DEEP:19-21:34</t>
         </is>
       </c>
       <c r="D575" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E575" s="2" t="inlineStr">
@@ -30366,12 +30366,12 @@
       </c>
       <c r="C576" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:34:21-23</t>
+          <t>MID_DEEP:21-23:34</t>
         </is>
       </c>
       <c r="D576" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E576" s="2" t="inlineStr">
@@ -30418,12 +30418,12 @@
       </c>
       <c r="C577" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:34:23-25</t>
+          <t>MID_DEEP:23-25:34</t>
         </is>
       </c>
       <c r="D577" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E577" s="2" t="inlineStr">
@@ -30470,12 +30470,12 @@
       </c>
       <c r="C578" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:34:25-27</t>
+          <t>MID_DEEP:25-27:34</t>
         </is>
       </c>
       <c r="D578" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E578" s="2" t="inlineStr">
@@ -30522,12 +30522,12 @@
       </c>
       <c r="C579" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:34:27-29</t>
+          <t>MID_DEEP:27-29:34</t>
         </is>
       </c>
       <c r="D579" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E579" s="2" t="inlineStr">
@@ -30574,12 +30574,12 @@
       </c>
       <c r="C580" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:35:0-1</t>
+          <t>MID_DEEP:0-1:35</t>
         </is>
       </c>
       <c r="D580" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E580" s="2" t="inlineStr">
@@ -30626,12 +30626,12 @@
       </c>
       <c r="C581" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:35:1-2</t>
+          <t>MID_DEEP:1-2:35</t>
         </is>
       </c>
       <c r="D581" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E581" s="2" t="inlineStr">
@@ -30678,12 +30678,12 @@
       </c>
       <c r="C582" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:35:2-3</t>
+          <t>MID_DEEP:2-3:35</t>
         </is>
       </c>
       <c r="D582" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E582" s="2" t="inlineStr">
@@ -30730,12 +30730,12 @@
       </c>
       <c r="C583" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:35:3-4</t>
+          <t>MID_DEEP:3-4:35</t>
         </is>
       </c>
       <c r="D583" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E583" s="2" t="inlineStr">
@@ -30782,12 +30782,12 @@
       </c>
       <c r="C584" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:35:4-5</t>
+          <t>MID_DEEP:4-5:35</t>
         </is>
       </c>
       <c r="D584" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E584" s="2" t="inlineStr">
@@ -30834,12 +30834,12 @@
       </c>
       <c r="C585" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:35:5-7</t>
+          <t>MID_DEEP:5-7:35</t>
         </is>
       </c>
       <c r="D585" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E585" s="2" t="inlineStr">
@@ -30886,12 +30886,12 @@
       </c>
       <c r="C586" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:35:7-9</t>
+          <t>MID_DEEP:7-9:35</t>
         </is>
       </c>
       <c r="D586" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E586" s="2" t="inlineStr">
@@ -30938,12 +30938,12 @@
       </c>
       <c r="C587" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:35:9-11</t>
+          <t>MID_DEEP:9-11:35</t>
         </is>
       </c>
       <c r="D587" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E587" s="2" t="inlineStr">
@@ -30990,12 +30990,12 @@
       </c>
       <c r="C588" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:35:11-13</t>
+          <t>MID_DEEP:11-13:35</t>
         </is>
       </c>
       <c r="D588" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E588" s="2" t="inlineStr">
@@ -31042,12 +31042,12 @@
       </c>
       <c r="C589" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:35:13-15</t>
+          <t>MID_DEEP:13-15:35</t>
         </is>
       </c>
       <c r="D589" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E589" s="2" t="inlineStr">
@@ -31094,12 +31094,12 @@
       </c>
       <c r="C590" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:35:15-17</t>
+          <t>MID_DEEP:15-17:35</t>
         </is>
       </c>
       <c r="D590" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E590" s="2" t="inlineStr">
@@ -31146,12 +31146,12 @@
       </c>
       <c r="C591" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:35:17-19</t>
+          <t>MID_DEEP:17-19:35</t>
         </is>
       </c>
       <c r="D591" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E591" s="2" t="inlineStr">
@@ -31198,12 +31198,12 @@
       </c>
       <c r="C592" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:35:19-21</t>
+          <t>MID_DEEP:19-21:35</t>
         </is>
       </c>
       <c r="D592" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E592" s="2" t="inlineStr">
@@ -31250,12 +31250,12 @@
       </c>
       <c r="C593" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:35:21-23</t>
+          <t>MID_DEEP:21-23:35</t>
         </is>
       </c>
       <c r="D593" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E593" s="2" t="inlineStr">
@@ -31302,12 +31302,12 @@
       </c>
       <c r="C594" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:35:23-25</t>
+          <t>MID_DEEP:23-25:35</t>
         </is>
       </c>
       <c r="D594" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E594" s="2" t="inlineStr">
@@ -31354,12 +31354,12 @@
       </c>
       <c r="C595" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:35:25-27</t>
+          <t>MID_DEEP:25-27:35</t>
         </is>
       </c>
       <c r="D595" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E595" s="2" t="inlineStr">
@@ -31406,12 +31406,12 @@
       </c>
       <c r="C596" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:35:27-29</t>
+          <t>MID_DEEP:27-29:35</t>
         </is>
       </c>
       <c r="D596" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E596" s="2" t="inlineStr">
@@ -31458,12 +31458,12 @@
       </c>
       <c r="C597" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:36:0-1</t>
+          <t>MID_DEEP:0-1:36</t>
         </is>
       </c>
       <c r="D597" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E597" s="2" t="inlineStr">
@@ -31510,12 +31510,12 @@
       </c>
       <c r="C598" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:36:1-2</t>
+          <t>MID_DEEP:1-2:36</t>
         </is>
       </c>
       <c r="D598" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E598" s="2" t="inlineStr">
@@ -31562,12 +31562,12 @@
       </c>
       <c r="C599" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:36:2-3</t>
+          <t>MID_DEEP:2-3:36</t>
         </is>
       </c>
       <c r="D599" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E599" s="2" t="inlineStr">
@@ -31614,12 +31614,12 @@
       </c>
       <c r="C600" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:36:3-4</t>
+          <t>MID_DEEP:3-4:36</t>
         </is>
       </c>
       <c r="D600" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E600" s="2" t="inlineStr">
@@ -31666,12 +31666,12 @@
       </c>
       <c r="C601" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:36:4-5</t>
+          <t>MID_DEEP:4-5:36</t>
         </is>
       </c>
       <c r="D601" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E601" s="2" t="inlineStr">
@@ -31718,12 +31718,12 @@
       </c>
       <c r="C602" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:36:5-7</t>
+          <t>MID_DEEP:5-7:36</t>
         </is>
       </c>
       <c r="D602" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E602" s="2" t="inlineStr">
@@ -31770,12 +31770,12 @@
       </c>
       <c r="C603" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:36:7-9</t>
+          <t>MID_DEEP:7-9:36</t>
         </is>
       </c>
       <c r="D603" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E603" s="2" t="inlineStr">
@@ -31822,12 +31822,12 @@
       </c>
       <c r="C604" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:36:9-11</t>
+          <t>MID_DEEP:9-11:36</t>
         </is>
       </c>
       <c r="D604" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E604" s="2" t="inlineStr">
@@ -31874,12 +31874,12 @@
       </c>
       <c r="C605" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:36:11-13</t>
+          <t>MID_DEEP:11-13:36</t>
         </is>
       </c>
       <c r="D605" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E605" s="2" t="inlineStr">
@@ -31926,12 +31926,12 @@
       </c>
       <c r="C606" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:36:13-15</t>
+          <t>MID_DEEP:13-15:36</t>
         </is>
       </c>
       <c r="D606" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E606" s="2" t="inlineStr">
@@ -31978,12 +31978,12 @@
       </c>
       <c r="C607" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:36:15-17</t>
+          <t>MID_DEEP:15-17:36</t>
         </is>
       </c>
       <c r="D607" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E607" s="2" t="inlineStr">
@@ -32030,12 +32030,12 @@
       </c>
       <c r="C608" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:36:17-19</t>
+          <t>MID_DEEP:17-19:36</t>
         </is>
       </c>
       <c r="D608" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E608" s="2" t="inlineStr">
@@ -32082,12 +32082,12 @@
       </c>
       <c r="C609" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:36:19-21</t>
+          <t>MID_DEEP:19-21:36</t>
         </is>
       </c>
       <c r="D609" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E609" s="2" t="inlineStr">
@@ -32134,12 +32134,12 @@
       </c>
       <c r="C610" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:36:21-23</t>
+          <t>MID_DEEP:21-23:36</t>
         </is>
       </c>
       <c r="D610" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E610" s="2" t="inlineStr">
@@ -32186,12 +32186,12 @@
       </c>
       <c r="C611" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:36:23-25</t>
+          <t>MID_DEEP:23-25:36</t>
         </is>
       </c>
       <c r="D611" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E611" s="2" t="inlineStr">
@@ -32238,12 +32238,12 @@
       </c>
       <c r="C612" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:36:25-27</t>
+          <t>MID_DEEP:25-27:36</t>
         </is>
       </c>
       <c r="D612" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E612" s="2" t="inlineStr">
@@ -32290,12 +32290,12 @@
       </c>
       <c r="C613" s="2" t="inlineStr">
         <is>
-          <t>MID_DEEP:36:27-29</t>
+          <t>MID_DEEP:27-29:36</t>
         </is>
       </c>
       <c r="D613" s="2" t="inlineStr">
         <is>
-          <t>Core Location Name:Core ID:depth</t>
+          <t>Core Location Name:depth:Core ID</t>
         </is>
       </c>
       <c r="E613" s="2" t="inlineStr">
